--- a/artfynd/A 643-2026 artfynd.xlsx
+++ b/artfynd/A 643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1189,6 +1189,126 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130625982</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57044</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarndammen, Kvarndammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529675</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6730708</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska spår i snön</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 643-2026 artfynd.xlsx
+++ b/artfynd/A 643-2026 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>130625982</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 643-2026 artfynd.xlsx
+++ b/artfynd/A 643-2026 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>130625982</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 643-2026 artfynd.xlsx
+++ b/artfynd/A 643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,74 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16030301</v>
+        <v>100832788</v>
       </c>
       <c r="B2" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lundbergs fäbodar, 420 m O bostadshuset, Dlr</t>
+          <t>Törnbergs väg/Lundbergs fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529679.4273876497</v>
+        <v>529438</v>
       </c>
       <c r="R2" t="n">
-        <v>6730197.286292877</v>
+        <v>6730506</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -811,16 +800,11 @@
         <v>100837393</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -858,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529519.7208080519</v>
+        <v>529520</v>
       </c>
       <c r="R3" t="n">
-        <v>6730714.8776761</v>
+        <v>6730715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -935,15 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100832788</v>
+        <v>130625982</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,47 +930,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Törnbergs väg/Lundbergs fäbodar, Dlr</t>
+          <t>Kvarndammen, Kvarndammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529437.1043089762</v>
+        <v>529675</v>
       </c>
       <c r="R4" t="n">
-        <v>6730506.154019083</v>
+        <v>6730708</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +992,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fjolårsfruktkropp</t>
+          <t>Färska spår i snön</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,27 +1027,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100832859</v>
+        <v>16030299</v>
       </c>
       <c r="B5" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,26 +1050,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>100141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1105,19 +1077,28 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Törnbergs väg/Lundbergs fäbodar, Dlr</t>
+          <t>Lundbergs fäbodar, 540 m O bostadshuset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529437.1043089762</v>
+        <v>529805</v>
       </c>
       <c r="R5" t="n">
-        <v>6730506.154019083</v>
+        <v>6730236</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1144,27 +1125,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fjolårsunge</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,22 +1155,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Falu Kommun</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Falu Kommun</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130625982</v>
+        <v>16030301</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>58829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,45 +1178,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarndammen, Kvarndammen, Dlr</t>
+          <t>Lundbergs fäbodar, 420 m O bostadshuset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529675</v>
+        <v>529679</v>
       </c>
       <c r="R6" t="n">
-        <v>6730708</v>
+        <v>6730197</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,27 +1253,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska spår i snön</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,15 +1283,258 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Falu Kommun</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson</t>
+          <t>Falu Kommun</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100826125</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lundbergs fäbodar, 500 m N om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>529457</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6730715</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100832859</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Törnbergs väg/Lundbergs fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529438</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6730506</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjolårsunge</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 643-2026 artfynd.xlsx
+++ b/artfynd/A 643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100832788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100837393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130625982</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16030299</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16030301</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1411,6 +1441,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100826125</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1535,8 +1570,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100832859</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>